--- a/SRF_CRF.xlsx
+++ b/SRF_CRF.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartContract\cypress\fixtures\File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dynamic Form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{50D91D68-7345-4B4C-84C1-0CEBAEBD5516}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E15D9044-B232-4F56-9998-1E3570A3E6EC}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9405" xr2:uid="{CADCD553-DC33-4550-83D9-40D5A3C16041}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="179021"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="93">
   <si>
     <t>name</t>
   </si>
@@ -129,9 +130,6 @@
     <t>CDA/NDA Available?</t>
   </si>
   <si>
-    <t>Not Applicable</t>
-  </si>
-  <si>
     <t>PO No/ Capex No</t>
   </si>
   <si>
@@ -189,9 +187,6 @@
     <t>Counterparty MSME No. Applicable?</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Provide MSME No.</t>
   </si>
   <si>
@@ -286,6 +281,30 @@
   </si>
   <si>
     <t>Plot No-D-2/1, Phase-II, Dahej Taluka Vagra, District Bharuch, Gujarat 392130, India</t>
+  </si>
+  <si>
+    <t>docx3</t>
+  </si>
+  <si>
+    <t>CDA</t>
+  </si>
+  <si>
+    <t>PO No</t>
+  </si>
+  <si>
+    <t>PO No.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>MSME No.</t>
+  </si>
+  <si>
+    <t>CIN No.</t>
+  </si>
+  <si>
+    <t>PO</t>
   </si>
 </sst>
 </file>
@@ -710,11 +729,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F8DC9E9-AB91-41C5-BABB-7257B851A741}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
-    <col min="2" max="2" width="83.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -734,7 +753,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -778,7 +797,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>13</v>
@@ -800,7 +819,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>13</v>
@@ -899,7 +918,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
@@ -907,87 +926,87 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
+      <c r="A19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
+        <v>82</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>7</v>
+        <v>82</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>13</v>
@@ -995,32 +1014,32 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="B28" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
@@ -1028,10 +1047,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>13</v>
@@ -1039,153 +1058,153 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>7</v>
+        <v>82</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>13</v>
+        <v>89</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>7</v>
+        <v>82</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="9">
-        <v>46053</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>7</v>
+        <v>58</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46053</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B37" s="10">
-        <v>46122</v>
-      </c>
-      <c r="C37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>61</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B38" s="10">
-        <v>48944</v>
+        <v>46122</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="10">
+        <v>48944</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B41" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>13</v>
+        <v>69</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>13</v>
@@ -1193,10 +1212,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" s="2">
-        <v>12345678</v>
+        <v>71</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>13</v>
@@ -1204,10 +1223,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
+      </c>
+      <c r="B45" s="2">
+        <v>12345678</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>13</v>
@@ -1215,24 +1234,90 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>78</v>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
